--- a/public/crawlability-barefootcozumel-september-2026.xlsx
+++ b/public/crawlability-barefootcozumel-september-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של barefootcozumel ב-SE Ranking (הסריקה האחרונה: 2024-04-09).</t>
+          <t>להריץ מחדש את ה-Website Audit של barefootcozumel ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-barefootcozumel-september-2026.xlsx
+++ b/public/crawlability-barefootcozumel-september-2026.xlsx
@@ -532,9 +532,9 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/public/crawlability-barefootcozumel-september-2026.xlsx
+++ b/public/crawlability-barefootcozumel-september-2026.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://barefootcozumel.com/private-snorkel-tour/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://barefootcozumel.com/private-snorkel-tour/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של barefootcozumel ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של barefootcozumel ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-barefootcozumel-september-2026.xlsx
+++ b/public/crawlability-barefootcozumel-september-2026.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,11 +67,6 @@
         <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -85,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -100,9 +95,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -509,7 +501,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>staging2.barefootcozumel.com: עותק מלא של האתר עם index, follow ו-canonical לעצמו. להגן בסיסמה (HTTP auth) או להגדיר X-Robots-Tag: noindex ו-Disallow: / בקובץ robots.txt של תת-הדומיין. נכון ל-27.09 לא נמצא באינדקס גוגל.</t>
+          <t>noindex על https://barefootcozumel.com/courses/ (638 קישורים נכנסים): לאשר שזו הכוונה, אחרת להסיר את ההנחיה.</t>
         </is>
       </c>
     </row>
@@ -517,14 +509,14 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד.</t>
+          <t>staging2.barefootcozumel.com: עותק מלא של האתר עם index, follow ו-canonical לעצמו. להגן בסיסמה (HTTP auth) או להגדיר X-Robots-Tag: noindex; לא לחסום ב-robots.txt. נכון ל-27.09 לא נמצא באינדקס גוגל.</t>
         </is>
       </c>
     </row>
@@ -532,14 +524,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://barefootcozumel.com/private-snorkel-tour/ (קישור נכנס אחד).</t>
+          <t>להסיר ממפת האתר כתובת אחת שמפנה (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
         </is>
       </c>
     </row>
@@ -554,22 +546,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של barefootcozumel ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>לאשר שהעמוד המוגדר noindex אכן אמור להישאר מחוץ לאינדקס.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://barefootcozumel.com/private-snorkel-tour/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -658,7 +635,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/private-snorkel-tour/</t>
         </is>
@@ -671,7 +648,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/snorkeling-tour/</t>
         </is>
@@ -682,7 +659,7 @@
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/fun-dives/</t>
         </is>
@@ -697,7 +674,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/snorkeling-tour/</t>
         </is>
@@ -779,7 +756,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/sitemap_index.xml</t>
         </is>
@@ -833,7 +810,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/sitemap_index.xml</t>
         </is>
@@ -855,7 +832,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/post-sitemap.xml</t>
         </is>
@@ -877,7 +854,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/page-sitemap.xml</t>
         </is>
@@ -899,7 +876,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/sitemap.xml</t>
         </is>
@@ -921,7 +898,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/wp-sitemap.xml</t>
         </is>
@@ -965,12 +942,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/dive-master-internship-old/</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/dive-master/</t>
         </is>
@@ -982,7 +959,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/</t>
         </is>
@@ -992,7 +969,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/ (0 הפניות)</t>
         </is>
@@ -1004,7 +981,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>http://barefootcozumel.com/</t>
         </is>
@@ -1014,7 +991,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/ (1 הפניות)</t>
         </is>
@@ -1026,7 +1003,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>https://www.barefootcozumel.com/</t>
         </is>
@@ -1036,7 +1013,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/ (1 הפניות)</t>
         </is>
@@ -1048,7 +1025,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>http://www.barefootcozumel.com/</t>
         </is>
@@ -1058,7 +1035,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/ (2 הפניות)</t>
         </is>
@@ -1111,7 +1088,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/</t>
         </is>
@@ -1129,7 +1106,7 @@
           <t>Certification &amp; Training Scuba Diving Courses in Cozumel</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>https://barefootcozumel.com/courses/</t>
         </is>
@@ -1233,7 +1210,7 @@
           <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>https://staging2.barefootcozumel.com/</t>
         </is>
@@ -1250,7 +1227,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>עותק מלא של האתר עם index, follow ו-canonical לעצמו. להגן בסיסמה (HTTP auth) או להגדיר X-Robots-Tag: noindex ו-Disallow: / בקובץ robots.txt של תת-הדומיין. נכון ל-27.09 לא נמצא באינדקס גוגל.</t>
+          <t>עותק מלא של האתר עם index, follow ו-canonical לעצמו. להגן בסיסמה (HTTP auth) או להגדיר X-Robots-Tag: noindex; לא לחסום ב-robots.txt. נכון ל-27.09 לא נמצא באינדקס גוגל.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
